--- a/docs/downloads/经营分_鲁西省区__菏泽片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__菏泽片区_2026-10-18.xlsx
@@ -1417,7 +1417,7 @@
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1659,22 +1659,22 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6617323639689709576</t>
+          <t>6601145944023009284</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>麗枫酒店（菏泽定陶店）</t>
+          <t>维也纳酒店（菏泽大学城店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>麗枫酒店(菏泽定陶店)</t>
+          <t>维也纳酒店(菏泽大学城店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1701,13 +1701,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1747,33 +1747,33 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6888904090332579844</t>
+          <t>6617323639689709576</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>麗枫酒店（菏泽郓城宋江武校店）</t>
+          <t>麗枫酒店（菏泽定陶店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>麗枫酒店(菏泽郓城宋江武校店)</t>
+          <t>麗枫酒店(菏泽定陶店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1789,13 +1789,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6854050314241263616</t>
+          <t>6888904090332579844</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>锦江之星品尚（菏泽郓城金河路酒店）</t>
+          <t>麗枫酒店（菏泽郓城宋江武校店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>锦江之星品尚(菏泽郓城金河路店)</t>
+          <t>麗枫酒店(菏泽郓城宋江武校店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1854,18 +1854,18 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7362039502652573711</t>
+          <t>6854050314241263616</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>希岸酒店（菏泽郓城高铁站店）</t>
+          <t>锦江之星品尚（菏泽郓城金河路酒店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>希岸酒店(郓城高铁站店)</t>
+          <t>锦江之星品尚(菏泽郓城金河路店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1942,18 +1942,18 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,稳房源,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -2099,22 +2099,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6601145944023009284</t>
+          <t>6937409074644387876</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳酒店（菏泽大学城店）</t>
+          <t>维也纳酒店（菏泽鑫凯国际家居广场店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳酒店(菏泽大学城店)</t>
+          <t>维也纳酒店(菏泽鑫凯国际家居广场店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,13 +2135,13 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2187,22 +2187,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6937409074644387876</t>
+          <t>7325704915811862565</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳酒店（菏泽鑫凯国际家居广场店）</t>
+          <t>锦江之星（成武大明湖路店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳酒店(菏泽鑫凯国际家居广场店)</t>
+          <t>锦江之星(成武大明湖路店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2223,19 +2223,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
+        <v>30</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>20</v>
+      </c>
+      <c r="P19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="n">
         <v>25</v>
-      </c>
-      <c r="N19" t="n">
-        <v>30</v>
-      </c>
-      <c r="O19" t="n">
-        <v>30</v>
-      </c>
-      <c r="P19" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2275,33 +2275,33 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7325704915811862565</t>
+          <t>7020239303439550494</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>锦江之星（成武大明湖路店）</t>
+          <t>希岸酒店（菏泽成武店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>锦江之星(成武大明湖路店)</t>
+          <t>希岸酒店(菏泽成武店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2311,19 +2311,19 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2363,33 +2363,33 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7020239303439550494</t>
+          <t>7362039502652573711</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>希岸酒店（菏泽成武店）</t>
+          <t>希岸酒店（菏泽郓城高铁站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>希岸酒店(菏泽成武店)</t>
+          <t>希岸酒店(郓城高铁站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>110</v>
       </c>
       <c r="I21" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2405,13 +2405,13 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
+        <v>30</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
         <v>25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>30</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -3177,7 +3177,7 @@
         <v>115</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>115</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
